--- a/RCS03N.xlsx
+++ b/RCS03N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="48">
   <si>
     <t/>
   </si>
@@ -35,12 +35,6 @@
   </si>
   <si>
     <t>S/GOOD PAHA&amp;DADA 1KG</t>
-  </si>
-  <si>
-    <t>20078645</t>
-  </si>
-  <si>
-    <t>S/GOOD PAHA&amp;DADA 450</t>
   </si>
   <si>
     <t>10017288</t>
@@ -553,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -634,7 +628,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>4</v>
@@ -645,16 +639,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>4</v>
@@ -674,47 +668,47 @@
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>4</v>
@@ -734,7 +728,7 @@
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>4</v>
@@ -754,7 +748,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>4</v>
@@ -774,7 +768,7 @@
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>4</v>
@@ -785,16 +779,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>4</v>
@@ -814,13 +808,13 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -834,27 +828,27 @@
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>4</v>
@@ -874,7 +868,7 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>4</v>
@@ -894,7 +888,7 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>4</v>
@@ -905,16 +899,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>4</v>
@@ -934,7 +928,7 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>4</v>
@@ -954,32 +948,12 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/RCS03N.xlsx
+++ b/RCS03N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="44">
   <si>
     <t/>
   </si>
@@ -31,72 +31,66 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
+    <t>10010749</t>
+  </si>
+  <si>
+    <t>S/G CHK.STK ORGNL200</t>
+  </si>
+  <si>
+    <t>10017288</t>
+  </si>
+  <si>
+    <t>SO GOOD SPIC.WING400</t>
+  </si>
+  <si>
+    <t>10019884</t>
+  </si>
+  <si>
+    <t>S/G CHK.NGT DINO 400</t>
+  </si>
+  <si>
+    <t>10020536</t>
+  </si>
+  <si>
+    <t>SO GOOD CHKN KRGE400</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10030051</t>
+  </si>
+  <si>
+    <t>S/GOOD BAKSO KUAH100</t>
+  </si>
+  <si>
+    <t>10030925</t>
+  </si>
+  <si>
+    <t>S/G CHK.NGT.ALPHB400</t>
+  </si>
+  <si>
+    <t>20002481</t>
+  </si>
+  <si>
+    <t>SO GOOD JETS 400G</t>
+  </si>
+  <si>
     <t>20051682</t>
   </si>
   <si>
     <t>S/GOOD PAHA&amp;DADA 1KG</t>
   </si>
   <si>
-    <t>10017288</t>
-  </si>
-  <si>
-    <t>SO GOOD SPIC.WING400</t>
+    <t>20045443</t>
+  </si>
+  <si>
+    <t>S/G CHK.STK PRM 400G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>10019884</t>
-  </si>
-  <si>
-    <t>S/G CHK.NGT DINO 400</t>
-  </si>
-  <si>
-    <t>10020536</t>
-  </si>
-  <si>
-    <t>SO GOOD CHKN KRGE400</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10010749</t>
-  </si>
-  <si>
-    <t>S/G CHK.STK ORGNL200</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10030051</t>
-  </si>
-  <si>
-    <t>S/GOOD BAKSO KUAH100</t>
-  </si>
-  <si>
-    <t>10030925</t>
-  </si>
-  <si>
-    <t>S/G CHK.NGT.ALPHB400</t>
-  </si>
-  <si>
-    <t>20002481</t>
-  </si>
-  <si>
-    <t>SO GOOD JETS 400G</t>
-  </si>
-  <si>
-    <t>20045443</t>
-  </si>
-  <si>
-    <t>S/G CHK.STK PRM 400G</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>20046992</t>
   </si>
   <si>
@@ -109,15 +103,24 @@
     <t>S/N CHK STC SDP 500</t>
   </si>
   <si>
+    <t>20076767</t>
+  </si>
+  <si>
+    <t>SG PREM SUASAGE 300G</t>
+  </si>
+  <si>
+    <t>20091453</t>
+  </si>
+  <si>
+    <t>SONICE SOSIS AYM 375</t>
+  </si>
+  <si>
     <t>20116088</t>
   </si>
   <si>
     <t>S/G CRSP BBQ WING400</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>20126960</t>
   </si>
   <si>
@@ -128,21 +131,6 @@
   </si>
   <si>
     <t>SG NGGET MAC&amp;CHSE400</t>
-  </si>
-  <si>
-    <t>20076767</t>
-  </si>
-  <si>
-    <t>SG PREM SUASAGE 300G</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20091453</t>
-  </si>
-  <si>
-    <t>SONICE SOSIS AYM 375</t>
   </si>
   <si>
     <t>20137492</t>
@@ -628,7 +616,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>4</v>
@@ -639,16 +627,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>4</v>
@@ -659,36 +647,36 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>4</v>
@@ -699,16 +687,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>4</v>
@@ -719,16 +707,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>4</v>
@@ -739,16 +727,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>4</v>
@@ -759,16 +747,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>4</v>
@@ -779,16 +767,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>4</v>
@@ -799,36 +787,36 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>4</v>
@@ -839,16 +827,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>4</v>
@@ -859,16 +847,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>4</v>
@@ -879,16 +867,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>4</v>
@@ -899,16 +887,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>4</v>
@@ -919,16 +907,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>4</v>
@@ -939,16 +927,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>4</v>
